--- a/REPORTE_TRASPASO_MSAVI_117_BLOQUES.xlsx
+++ b/REPORTE_TRASPASO_MSAVI_117_BLOQUES.xlsx
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>CONFORME: 6 · CORREGIDO: 1 · NO SUSTANTIVA: 1 · SUSTANTIVA: 1</t>
+          <t>CONFORME: 6 · CORREGIDO: 1 · NO SUSTANTIVA: 1 · SUSTANTIVA: 2</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
-          <t>CONFORME: 6 · CORREGIDO: 1 · NO SUSTANTIVA: 4 · SUSTANTIVA: 2</t>
+          <t>CONFORME: 6 · CORREGIDO: 1 · NO SUSTANTIVA: 4 · SUSTANTIVA: 3</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="Q51" s="12" t="inlineStr">
         <is>
-          <t>CONFORME: 4 · CORREGIDO: 1 · NO SUSTANTIVA: 2 · SUSTANTIVA: 8</t>
+          <t>CONFORME: 4 · CORREGIDO: 3 · NO SUSTANTIVA: 2 · SUSTANTIVA: 8</t>
         </is>
       </c>
     </row>
